--- a/docs/sample-data/Template_MCQs.xlsx
+++ b/docs/sample-data/Template_MCQs.xlsx
@@ -85,17 +85,28 @@
       <name val="Calibri"/>
       <sz val="11.0"/>
       <b val="true"/>
+      <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="darkGray"/>
     </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor rgb="1A2B4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="1A2B4A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -103,13 +114,18 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
